--- a/public/questions.xlsx
+++ b/public/questions.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="170">
   <si>
     <t>category</t>
   </si>
@@ -105,7 +105,7 @@
     <t>¿Cuántas horas tuvo el siglo XX?</t>
   </si>
   <si>
-    <t>¿Cuántos minutos funciona un coche medio en España antes de acabar en el desguace?</t>
+    <t>¿Cuántos minutos se pasa encendido de media un coche en España antes de acabar en el desguace?</t>
   </si>
   <si>
     <t>¿Cuántas horas de Netflix han visto entre todos los españoles entre 2020 y 2025?</t>
@@ -138,7 +138,7 @@
     <t>¿Cuántos kilos pesan entre todos los españoles?</t>
   </si>
   <si>
-    <t>¿Cuántos kilos pesan entre todos los teléfonos móviles de España?</t>
+    <t>¿Cuántos kilos pesan entre todos los teléfonos móviles de España que están encendidos ahora mismo?</t>
   </si>
   <si>
     <t>¿Cuántos kilos pesa la Puerta de Alcalá?</t>
@@ -445,9 +445,6 @@
   </si>
   <si>
     <t>¿Cuántas piezas de LEGO existen actualmente en el mundo (fabricadas desde su inicio)?</t>
-  </si>
-  <si>
-    <t>¿Cuántas veces late el corazón de un ratón de campo en un solo minuto?</t>
   </si>
   <si>
     <t>¿Cuántos litros de agua se evaporan de una piscina olímpica en un día caluroso de agosto?</t>
@@ -8223,195 +8220,193 @@
     </row>
     <row r="3">
       <c r="A3" s="11"/>
-      <c r="B3" s="14" t="s">
-        <v>143</v>
-      </c>
+      <c r="B3" s="14"/>
     </row>
     <row r="4">
       <c r="A4" s="11"/>
       <c r="B4" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11"/>
       <c r="B5" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11"/>
       <c r="B6" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11"/>
       <c r="B7" s="14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11"/>
       <c r="B8" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11"/>
       <c r="B9" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11"/>
       <c r="B10" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11"/>
       <c r="B11" s="14" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11"/>
       <c r="B12" s="14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11"/>
       <c r="B13" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11"/>
       <c r="B14" s="14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11"/>
       <c r="B15" s="14" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11"/>
       <c r="B16" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11"/>
       <c r="B17" s="14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11"/>
       <c r="B18" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11"/>
       <c r="B19" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11"/>
       <c r="B20" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11"/>
       <c r="B21" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11"/>
       <c r="B22" s="14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11"/>
       <c r="B23" s="14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11"/>
       <c r="B24" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11"/>
       <c r="B25" s="14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11"/>
       <c r="B26" s="14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11"/>
       <c r="B27" s="14" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11"/>
       <c r="B28" s="14" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11"/>
       <c r="B29" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11"/>
       <c r="B30" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/public/questions.xlsx
+++ b/public/questions.xlsx
@@ -126,7 +126,7 @@
     <t>¿Cuántos granos de arroz caben en una botella de vino?</t>
   </si>
   <si>
-    <t>¿Cuántas bolas de pingpong se necesitan para cubrir el césped del Santiago Bernabéu?</t>
+    <t>¿Cuántas bolas de pingpong se necesitan para cubrir el césped del campo de fútbol Santiago Bernabéu?</t>
   </si>
   <si>
     <t>¿Cuántas bolas de pingpong se necesitan para llenar una piscina olímpica?</t>

--- a/public/questions.xlsx
+++ b/public/questions.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="171">
   <si>
     <t>category</t>
   </si>
@@ -60,6 +60,9 @@
     <t>q_p05_p95</t>
   </si>
   <si>
+    <t>difficulty</t>
+  </si>
+  <si>
     <t>question</t>
   </si>
   <si>
@@ -129,7 +132,7 @@
     <t>¿Cuántas bolas de pingpong se necesitan para cubrir el césped del campo de fútbol Santiago Bernabéu?</t>
   </si>
   <si>
-    <t>¿Cuántas bolas de pingpong se necesitan para llenar una piscina olímpica?</t>
+    <t>¿Cuántos cartuchos de la Nintendo Switch harían falta para cubrir por completo el estanque de agua del Retiro?</t>
   </si>
   <si>
     <t>¿Cuántos estadios como el Bernabéu podrías cubrir con todo el papel y cartón que usamos desde los hogares de los españoles?</t>
@@ -1479,8 +1482,11 @@
       <c r="D1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="4" t="s">
         <v>14</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="2">
@@ -1497,8 +1503,11 @@
         <f t="shared" ref="D2:D33" si="1">C2/B2</f>
         <v>1.5</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>15</v>
+      <c r="E2" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -1515,8 +1524,11 @@
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>16</v>
+      <c r="E3" s="5">
+        <v>2.1</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -1533,8 +1545,11 @@
         <f t="shared" si="1"/>
         <v>2.4</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>17</v>
+      <c r="E4" s="5">
+        <v>2.3</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -1551,8 +1566,11 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>18</v>
+      <c r="E5" s="5">
+        <v>2.2</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -1569,8 +1587,11 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>19</v>
+      <c r="E6" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -1587,8 +1608,11 @@
         <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>20</v>
+      <c r="E7" s="5">
+        <v>2.8</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -1605,8 +1629,11 @@
         <f t="shared" si="1"/>
         <v>2.142857143</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>21</v>
+      <c r="E8" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -1623,8 +1650,11 @@
         <f t="shared" si="1"/>
         <v>1.428571429</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>22</v>
+      <c r="E9" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -1641,8 +1671,11 @@
         <f t="shared" si="1"/>
         <v>1.0625</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>23</v>
+      <c r="E10" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="11">
@@ -1659,8 +1692,11 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>24</v>
+      <c r="E11" s="5">
+        <v>2.4</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="12">
@@ -1677,8 +1713,11 @@
         <f t="shared" si="1"/>
         <v>2.083333333</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>25</v>
+      <c r="E12" s="5">
+        <v>3.2</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="13">
@@ -1695,8 +1734,11 @@
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>26</v>
+      <c r="E13" s="5">
+        <v>3.8</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="14">
@@ -1713,8 +1755,11 @@
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>27</v>
+      <c r="E14" s="5">
+        <v>2.6</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -1731,8 +1776,11 @@
         <f t="shared" si="1"/>
         <v>1.011494253</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>28</v>
+      <c r="E15" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -1749,8 +1797,11 @@
         <f t="shared" si="1"/>
         <v>1.75</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>29</v>
+      <c r="E16" s="5">
+        <v>2.7</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1767,8 +1818,11 @@
         <f t="shared" si="1"/>
         <v>1.75</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>30</v>
+      <c r="E17" s="5">
+        <v>3.3</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="18">
@@ -1785,8 +1839,11 @@
         <f t="shared" si="1"/>
         <v>1.8</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>31</v>
+      <c r="E18" s="5">
+        <v>1.8</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="19">
@@ -1803,8 +1860,11 @@
         <f t="shared" si="1"/>
         <v>1.25</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>32</v>
+      <c r="E19" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="20">
@@ -1821,8 +1881,11 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>33</v>
+      <c r="E20" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="21">
@@ -1839,8 +1902,11 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>34</v>
+      <c r="E21" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="22">
@@ -1857,8 +1923,11 @@
         <f t="shared" si="1"/>
         <v>1.6</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>35</v>
+      <c r="E22" s="5">
+        <v>1.9</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="23">
@@ -1875,8 +1944,11 @@
         <f t="shared" si="1"/>
         <v>1.375</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>36</v>
+      <c r="E23" s="5">
+        <v>2.1</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="24">
@@ -1884,17 +1956,20 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="9">
-        <v>4.0E7</v>
+        <v>5.0E7</v>
       </c>
       <c r="C24" s="9">
-        <v>8.0E7</v>
+        <v>7.0E7</v>
       </c>
       <c r="D24" s="10">
         <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>37</v>
+        <v>1.4</v>
+      </c>
+      <c r="E24" s="5">
+        <v>2.2</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="25">
@@ -1911,8 +1986,11 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>38</v>
+      <c r="E25" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="26">
@@ -1929,8 +2007,11 @@
         <f t="shared" si="1"/>
         <v>1.25</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>39</v>
+      <c r="E26" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="27">
@@ -1947,8 +2028,11 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>40</v>
+      <c r="E27" s="5">
+        <v>2.2</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="28">
@@ -1965,8 +2049,11 @@
         <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>41</v>
+      <c r="E28" s="5">
+        <v>3.2</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="29">
@@ -1983,8 +2070,11 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="E29" s="5" t="s">
-        <v>42</v>
+      <c r="E29" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="30">
@@ -2001,8 +2091,11 @@
         <f t="shared" si="1"/>
         <v>1.4</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>43</v>
+      <c r="E30" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="31">
@@ -2019,8 +2112,11 @@
         <f t="shared" si="1"/>
         <v>1.75</v>
       </c>
-      <c r="E31" s="5" t="s">
-        <v>44</v>
+      <c r="E31" s="5">
+        <v>2.4</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="32">
@@ -2037,8 +2133,11 @@
         <f t="shared" si="1"/>
         <v>2.4</v>
       </c>
-      <c r="E32" s="5" t="s">
-        <v>45</v>
+      <c r="E32" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="33">
@@ -2055,8 +2154,11 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>46</v>
+      <c r="E33" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="34">
@@ -2064,28 +2166,28 @@
       <c r="B34" s="12"/>
       <c r="C34" s="13"/>
       <c r="D34" s="10"/>
-      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
     </row>
     <row r="35">
       <c r="A35" s="11"/>
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
       <c r="D35" s="10"/>
-      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
     </row>
     <row r="36">
       <c r="A36" s="11"/>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
       <c r="D36" s="10"/>
-      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
     </row>
     <row r="37">
       <c r="A37" s="11"/>
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
       <c r="D37" s="10"/>
-      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
     </row>
     <row r="38">
       <c r="A38" s="11">
@@ -2101,8 +2203,11 @@
         <f t="shared" ref="D38:D67" si="2">C38/B38</f>
         <v>2.692307692</v>
       </c>
-      <c r="E38" s="14" t="s">
-        <v>47</v>
+      <c r="E38" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="F38" s="14" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="39">
@@ -2119,8 +2224,11 @@
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="E39" s="14" t="s">
-        <v>48</v>
+      <c r="E39" s="5">
+        <v>2.2</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="40">
@@ -2137,8 +2245,11 @@
         <f t="shared" si="2"/>
         <v>1.6</v>
       </c>
-      <c r="E40" s="14" t="s">
-        <v>49</v>
+      <c r="E40" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="F40" s="14" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="41">
@@ -2155,8 +2266,11 @@
         <f t="shared" si="2"/>
         <v>4.444444444</v>
       </c>
-      <c r="E41" s="14" t="s">
-        <v>50</v>
+      <c r="E41" s="5">
+        <v>2.6</v>
+      </c>
+      <c r="F41" s="14" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="42">
@@ -2173,8 +2287,11 @@
         <f t="shared" si="2"/>
         <v>3.888888889</v>
       </c>
-      <c r="E42" s="14" t="s">
-        <v>51</v>
+      <c r="E42" s="5">
+        <v>2.3</v>
+      </c>
+      <c r="F42" s="14" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="43">
@@ -2191,8 +2308,11 @@
         <f t="shared" si="2"/>
         <v>1.333333333</v>
       </c>
-      <c r="E43" s="14" t="s">
-        <v>52</v>
+      <c r="E43" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="F43" s="14" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="44">
@@ -2209,8 +2329,11 @@
         <f t="shared" si="2"/>
         <v>1.071428571</v>
       </c>
-      <c r="E44" s="14" t="s">
-        <v>53</v>
+      <c r="E44" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="F44" s="14" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="45">
@@ -2227,8 +2350,11 @@
         <f t="shared" si="2"/>
         <v>2.666666667</v>
       </c>
-      <c r="E45" s="14" t="s">
-        <v>54</v>
+      <c r="E45" s="5">
+        <v>1.1</v>
+      </c>
+      <c r="F45" s="14" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="46">
@@ -2245,8 +2371,11 @@
         <f t="shared" si="2"/>
         <v>2.272727273</v>
       </c>
-      <c r="E46" s="14" t="s">
-        <v>55</v>
+      <c r="E46" s="5">
+        <v>1.8</v>
+      </c>
+      <c r="F46" s="14" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="47">
@@ -2263,8 +2392,11 @@
         <f t="shared" si="2"/>
         <v>2.857142857</v>
       </c>
-      <c r="E47" s="14" t="s">
-        <v>56</v>
+      <c r="E47" s="5">
+        <v>1.7</v>
+      </c>
+      <c r="F47" s="14" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="48">
@@ -2281,8 +2413,11 @@
         <f t="shared" si="2"/>
         <v>2.266666667</v>
       </c>
-      <c r="E48" s="14" t="s">
-        <v>57</v>
+      <c r="E48" s="5">
+        <v>2.1</v>
+      </c>
+      <c r="F48" s="14" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="49">
@@ -2299,8 +2434,11 @@
         <f t="shared" si="2"/>
         <v>1.75</v>
       </c>
-      <c r="E49" s="14" t="s">
-        <v>58</v>
+      <c r="E49" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="F49" s="14" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="50">
@@ -2317,8 +2455,11 @@
         <f t="shared" si="2"/>
         <v>1.105263158</v>
       </c>
-      <c r="E50" s="14" t="s">
-        <v>59</v>
+      <c r="E50" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="F50" s="14" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="51">
@@ -2335,8 +2476,11 @@
         <f t="shared" si="2"/>
         <v>2.5</v>
       </c>
-      <c r="E51" s="14" t="s">
-        <v>60</v>
+      <c r="E51" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="F51" s="14" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="52">
@@ -2353,8 +2497,11 @@
         <f t="shared" si="2"/>
         <v>2.454545455</v>
       </c>
-      <c r="E52" s="14" t="s">
-        <v>61</v>
+      <c r="E52" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F52" s="14" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="53">
@@ -2371,8 +2518,11 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="E53" s="14" t="s">
-        <v>62</v>
+      <c r="E53" s="5">
+        <v>2.7</v>
+      </c>
+      <c r="F53" s="14" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="54">
@@ -2389,8 +2539,11 @@
         <f t="shared" si="2"/>
         <v>2.666666667</v>
       </c>
-      <c r="E54" s="14" t="s">
-        <v>63</v>
+      <c r="E54" s="5">
+        <v>2.4</v>
+      </c>
+      <c r="F54" s="14" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="55">
@@ -2407,8 +2560,11 @@
         <f t="shared" si="2"/>
         <v>1.5</v>
       </c>
-      <c r="E55" s="14" t="s">
-        <v>64</v>
+      <c r="E55" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="F55" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="56">
@@ -2425,8 +2581,11 @@
         <f t="shared" si="2"/>
         <v>2.058823529</v>
       </c>
-      <c r="E56" s="14" t="s">
-        <v>65</v>
+      <c r="E56" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="F56" s="14" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="57">
@@ -2443,8 +2602,11 @@
         <f t="shared" si="2"/>
         <v>2.533333333</v>
       </c>
-      <c r="E57" s="14" t="s">
-        <v>66</v>
+      <c r="E57" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="F57" s="14" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="58">
@@ -2461,8 +2623,11 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="E58" s="5" t="s">
-        <v>67</v>
+      <c r="E58" s="5">
+        <v>1.6</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="59">
@@ -2479,8 +2644,11 @@
         <f t="shared" si="2"/>
         <v>1.060240964</v>
       </c>
-      <c r="E59" s="5" t="s">
-        <v>68</v>
+      <c r="E59" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="60">
@@ -2497,8 +2665,11 @@
         <f t="shared" si="2"/>
         <v>2.5</v>
       </c>
-      <c r="E60" s="5" t="s">
-        <v>69</v>
+      <c r="E60" s="5">
+        <v>2.8</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="61">
@@ -2515,8 +2686,11 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="E61" s="5" t="s">
-        <v>70</v>
+      <c r="E61" s="5">
+        <v>3.6</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="62">
@@ -2533,8 +2707,11 @@
         <f t="shared" si="2"/>
         <v>3.333333333</v>
       </c>
-      <c r="E62" s="5" t="s">
-        <v>71</v>
+      <c r="E62" s="5">
+        <v>3.3</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="63">
@@ -2551,8 +2728,11 @@
         <f t="shared" si="2"/>
         <v>2.5</v>
       </c>
-      <c r="E63" s="5" t="s">
-        <v>72</v>
+      <c r="E63" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="64">
@@ -2569,8 +2749,11 @@
         <f t="shared" si="2"/>
         <v>2.222222222</v>
       </c>
-      <c r="E64" s="5" t="s">
-        <v>73</v>
+      <c r="E64" s="5">
+        <v>2.9</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="65">
@@ -2587,8 +2770,11 @@
         <f t="shared" si="2"/>
         <v>2.4</v>
       </c>
-      <c r="E65" s="5" t="s">
-        <v>74</v>
+      <c r="E65" s="5">
+        <v>3.2</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="66">
@@ -2605,8 +2791,11 @@
         <f t="shared" si="2"/>
         <v>3.2</v>
       </c>
-      <c r="E66" s="5" t="s">
-        <v>75</v>
+      <c r="E66" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="67">
@@ -2623,8 +2812,11 @@
         <f t="shared" si="2"/>
         <v>3.125</v>
       </c>
-      <c r="E67" s="5" t="s">
-        <v>76</v>
+      <c r="E67" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="68">
@@ -7416,7 +7608,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>10</v>
@@ -7446,7 +7638,7 @@
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B2" s="5">
         <v>1.0</v>
@@ -7454,7 +7646,7 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B3" s="5">
         <v>17.0</v>
@@ -7462,7 +7654,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B4" s="5">
         <v>6.0</v>
@@ -7470,7 +7662,7 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B5" s="5">
         <v>22.0</v>
@@ -7478,7 +7670,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B6" s="5">
         <v>11.0</v>
@@ -7486,7 +7678,7 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B7" s="5">
         <v>27.0</v>
@@ -7494,7 +7686,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="5">
         <v>16.0</v>
@@ -7502,7 +7694,7 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B9" s="5">
         <v>32.0</v>
@@ -7510,7 +7702,7 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B10" s="5">
         <v>13.0</v>
@@ -7518,7 +7710,7 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B11" s="5">
         <v>29.0</v>
@@ -7526,7 +7718,7 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B12" s="5">
         <v>2.0</v>
@@ -7534,7 +7726,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B13" s="5">
         <v>18.0</v>
@@ -7542,7 +7734,7 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B14" s="5">
         <v>7.0</v>
@@ -7550,7 +7742,7 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B15" s="5">
         <v>23.0</v>
@@ -7558,7 +7750,7 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B16" s="5">
         <v>12.0</v>
@@ -7566,7 +7758,7 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B17" s="5">
         <v>28.0</v>
@@ -7574,7 +7766,7 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B18" s="5">
         <v>9.0</v>
@@ -7582,7 +7774,7 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B19" s="5">
         <v>25.0</v>
@@ -7590,7 +7782,7 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B20" s="5">
         <v>14.0</v>
@@ -7598,7 +7790,7 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B21" s="5">
         <v>30.0</v>
@@ -7606,7 +7798,7 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B22" s="5">
         <v>3.0</v>
@@ -7614,7 +7806,7 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B23" s="5">
         <v>19.0</v>
@@ -7622,7 +7814,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B24" s="5">
         <v>8.0</v>
@@ -7630,7 +7822,7 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B25" s="5">
         <v>24.0</v>
@@ -7638,7 +7830,7 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B26" s="5">
         <v>5.0</v>
@@ -7646,7 +7838,7 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B27" s="5">
         <v>21.0</v>
@@ -7654,7 +7846,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B28" s="5">
         <v>10.0</v>
@@ -7662,7 +7854,7 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B29" s="5">
         <v>26.0</v>
@@ -7670,7 +7862,7 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B30" s="5">
         <v>15.0</v>
@@ -7678,7 +7870,7 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B31" s="5">
         <v>31.0</v>
@@ -7686,7 +7878,7 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B32" s="5">
         <v>4.0</v>
@@ -7694,7 +7886,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B33" s="5">
         <v>20.0</v>
@@ -7717,7 +7909,7 @@
         <v>1.0</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2">
@@ -7725,7 +7917,7 @@
         <v>2.0</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3">
@@ -7733,7 +7925,7 @@
         <v>3.0</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4">
@@ -7741,7 +7933,7 @@
         <v>4.0</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5">
@@ -7749,7 +7941,7 @@
         <v>5.0</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6">
@@ -7757,7 +7949,7 @@
         <v>6.0</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7">
@@ -7765,7 +7957,7 @@
         <v>13.0</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8">
@@ -7773,7 +7965,7 @@
         <v>14.0</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9">
@@ -7781,7 +7973,7 @@
         <v>15.0</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10">
@@ -7789,7 +7981,7 @@
         <v>16.0</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11">
@@ -7797,7 +7989,7 @@
         <v>17.0</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -7805,7 +7997,7 @@
         <v>18.0</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -7813,7 +8005,7 @@
         <v>19.0</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -7821,7 +8013,7 @@
         <v>20.0</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -7829,7 +8021,7 @@
         <v>21.0</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16">
@@ -7837,7 +8029,7 @@
         <v>22.0</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -7845,7 +8037,7 @@
         <v>23.0</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18">
@@ -7853,7 +8045,7 @@
         <v>24.0</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
@@ -7861,7 +8053,7 @@
         <v>25.0</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20">
@@ -7869,7 +8061,7 @@
         <v>26.0</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21">
@@ -7883,7 +8075,7 @@
         <v>28.0</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23">
@@ -7891,7 +8083,7 @@
         <v>29.0</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24">
@@ -7899,7 +8091,7 @@
         <v>30.0</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25">
@@ -7907,7 +8099,7 @@
         <v>31.0</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26">
@@ -7915,7 +8107,7 @@
         <v>32.0</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27">
@@ -7923,7 +8115,7 @@
         <v>101.0</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28">
@@ -7931,7 +8123,7 @@
         <v>104.0</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29">
@@ -7939,7 +8131,7 @@
         <v>105.0</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30">
@@ -7947,7 +8139,7 @@
         <v>106.0</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31">
@@ -7955,7 +8147,7 @@
         <v>107.0</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32">
@@ -7963,7 +8155,7 @@
         <v>108.0</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33">
@@ -7971,7 +8163,7 @@
         <v>109.0</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34">
@@ -7979,7 +8171,7 @@
         <v>110.0</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35">
@@ -7991,7 +8183,7 @@
         <v>112.0</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37">
@@ -7999,7 +8191,7 @@
         <v>113.0</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="38">
@@ -8007,7 +8199,7 @@
         <v>115.0</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="39">
@@ -8015,7 +8207,7 @@
         <v>116.0</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="40">
@@ -8023,7 +8215,7 @@
         <v>117.0</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="41">
@@ -8031,7 +8223,7 @@
         <v>118.0</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="42">
@@ -8039,7 +8231,7 @@
         <v>119.0</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="43">
@@ -8047,7 +8239,7 @@
         <v>120.0</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44">
@@ -8055,7 +8247,7 @@
         <v>121.0</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="45">
@@ -8063,7 +8255,7 @@
         <v>123.0</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="46">
@@ -8071,7 +8263,7 @@
         <v>124.0</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47">
@@ -8079,7 +8271,7 @@
         <v>126.0</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="48">
@@ -8087,7 +8279,7 @@
         <v>127.0</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="49">
@@ -8095,7 +8287,7 @@
         <v>128.0</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="50">
@@ -8103,7 +8295,7 @@
         <v>129.0</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="51">
@@ -8111,7 +8303,7 @@
         <v>130.0</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="52">
@@ -8119,7 +8311,7 @@
         <v>131.0</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="53">
@@ -8127,7 +8319,7 @@
         <v>132.0</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="54">
@@ -8135,7 +8327,7 @@
         <v>133.0</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="55">
@@ -8143,7 +8335,7 @@
         <v>134.0</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="56">
@@ -8151,7 +8343,7 @@
         <v>135.0</v>
       </c>
       <c r="B56" s="14" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="57">
@@ -8159,7 +8351,7 @@
         <v>136.0</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="58">
@@ -8167,7 +8359,7 @@
         <v>137.0</v>
       </c>
       <c r="B58" s="14" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="59">
@@ -8175,7 +8367,7 @@
         <v>138.0</v>
       </c>
       <c r="B59" s="14" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="60">
@@ -8183,7 +8375,7 @@
         <v>139.0</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="61">
@@ -8191,7 +8383,7 @@
         <v>10</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -8209,13 +8401,13 @@
     <row r="1">
       <c r="A1" s="11"/>
       <c r="B1" s="14" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="11"/>
       <c r="B2" s="14" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3">
@@ -8225,188 +8417,188 @@
     <row r="4">
       <c r="A4" s="11"/>
       <c r="B4" s="14" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11"/>
       <c r="B5" s="14" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11"/>
       <c r="B6" s="14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11"/>
       <c r="B7" s="14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11"/>
       <c r="B8" s="14" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11"/>
       <c r="B9" s="14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11"/>
       <c r="B10" s="14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11"/>
       <c r="B11" s="14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11"/>
       <c r="B12" s="14" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11"/>
       <c r="B13" s="14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11"/>
       <c r="B14" s="14" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11"/>
       <c r="B15" s="14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11"/>
       <c r="B16" s="14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11"/>
       <c r="B17" s="14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11"/>
       <c r="B18" s="14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11"/>
       <c r="B19" s="14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11"/>
       <c r="B20" s="14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11"/>
       <c r="B21" s="14" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11"/>
       <c r="B22" s="14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11"/>
       <c r="B23" s="14" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11"/>
       <c r="B24" s="14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11"/>
       <c r="B25" s="14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11"/>
       <c r="B26" s="14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11"/>
       <c r="B27" s="14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11"/>
       <c r="B28" s="14" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11"/>
       <c r="B29" s="14" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11"/>
       <c r="B30" s="14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/public/questions.xlsx
+++ b/public/questions.xlsx
@@ -9089,7 +9089,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="2" max="2" width="16.63"/>
-    <col customWidth="1" min="4" max="4" width="19.38"/>
+    <col customWidth="1" min="4" max="4" width="22.38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9102,7 +9102,7 @@
       <c r="C1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="2"/>
+      <c r="D1" s="4"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>

--- a/public/questions.xlsx
+++ b/public/questions.xlsx
@@ -1623,7 +1623,7 @@
         <v>4</v>
       </c>
       <c r="H3" s="15">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="I3" s="15" t="s">
         <v>20</v>
@@ -1680,7 +1680,7 @@
         <v>4</v>
       </c>
       <c r="H4" s="15">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="I4" s="15" t="s">
         <v>21</v>
@@ -1737,7 +1737,7 @@
         <v>2</v>
       </c>
       <c r="H5" s="15">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I5" s="15" t="s">
         <v>22</v>
@@ -1851,7 +1851,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="15">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I7" s="15" t="s">
         <v>24</v>
@@ -2022,7 +2022,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="15">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>27</v>
@@ -2307,7 +2307,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>32</v>
@@ -2745,11 +2745,11 @@
         <v>4000000.0</v>
       </c>
       <c r="C23" s="11">
-        <v>5500000.0</v>
+        <v>6000000.0</v>
       </c>
       <c r="D23" s="12">
         <f t="shared" si="1"/>
-        <v>1.375</v>
+        <v>1.5</v>
       </c>
       <c r="E23" s="13">
         <v>1069.0</v>
@@ -2820,7 +2820,7 @@
         <v>4</v>
       </c>
       <c r="H24" s="15">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>41</v>
@@ -2877,7 +2877,7 @@
         <v>4</v>
       </c>
       <c r="H25" s="10">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>42</v>
@@ -3048,7 +3048,7 @@
         <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>45</v>
@@ -3276,7 +3276,7 @@
         <v>4</v>
       </c>
       <c r="H32" s="10">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="I32" s="10" t="s">
         <v>49</v>
@@ -3431,7 +3431,7 @@
         <v>3</v>
       </c>
       <c r="H36" s="22">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="I36" s="23" t="s">
         <v>53</v>
@@ -3463,7 +3463,7 @@
         <v>3</v>
       </c>
       <c r="H37" s="22">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="I37" s="23" t="s">
         <v>54</v>
@@ -3719,7 +3719,7 @@
         <v>2</v>
       </c>
       <c r="H45" s="22">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I45" s="23" t="s">
         <v>62</v>
@@ -4231,7 +4231,7 @@
         <v>2</v>
       </c>
       <c r="H61" s="20">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I61" s="5" t="s">
         <v>78</v>
@@ -4295,16 +4295,11 @@
         <v>2</v>
       </c>
       <c r="H63" s="20">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I63" s="5" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="64">
-      <c r="B64" s="24"/>
-      <c r="C64" s="24"/>
-      <c r="D64" s="25"/>
     </row>
     <row r="65">
       <c r="B65" s="24"/>
@@ -9075,6 +9070,11 @@
       <c r="B1018" s="24"/>
       <c r="C1018" s="24"/>
       <c r="D1018" s="25"/>
+    </row>
+    <row r="1019">
+      <c r="B1019" s="24"/>
+      <c r="C1019" s="24"/>
+      <c r="D1019" s="25"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/public/questions.xlsx
+++ b/public/questions.xlsx
@@ -189,7 +189,7 @@
     <t>¿Cuántas palabras pronuncia una persona media a lo largo de un día normal?</t>
   </si>
   <si>
-    <t>Uno de cada _________ españoles ha nacido un 28 de febrero.</t>
+    <t>Uno de cada _________ españoles ha nacido un 29 de febrero.</t>
   </si>
   <si>
     <t>¿Cuántas calorías quema un corredor de maratón durante los 42 kilómetros de carrera?</t>
